--- a/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
+++ b/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3861" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3860" uniqueCount="678">
   <si>
     <t xml:space="preserve">class_name/model</t>
   </si>
@@ -2005,27 +2005,30 @@
     <t xml:space="preserve">BOTTOM</t>
   </si>
   <si>
-    <t xml:space="preserve">9.624e-11 (8)</t>
+    <t xml:space="preserve">1.245e-6 (7)</t>
   </si>
   <si>
     <t xml:space="preserve">1.465e-6 (6)</t>
   </si>
   <si>
-    <t xml:space="preserve">3.382e-14 (10)</t>
+    <t xml:space="preserve">5.972e-9 (9)</t>
   </si>
   <si>
     <t xml:space="preserve">4.066e-6 (5)</t>
   </si>
   <si>
+    <t xml:space="preserve">7.123e-2 (3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">8.892e-3 (5)</t>
   </si>
   <si>
-    <t xml:space="preserve">6.743e-3 (3)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.082e-4 (4)</t>
   </si>
   <si>
+    <t xml:space="preserve">7.889e-3 (4)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.521e-6 (5)</t>
   </si>
   <si>
@@ -2035,25 +2038,25 @@
     <t xml:space="preserve">1.638e-5 (4)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.348e-11 (10)</t>
+    <t xml:space="preserve">8.073e-8 (10)</t>
   </si>
   <si>
     <t xml:space="preserve">6.967e-3 (3)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.128e-7 (7)</t>
+    <t xml:space="preserve">2.407e-5 (7)</t>
   </si>
   <si>
     <t xml:space="preserve">3.967e-6 (4)</t>
   </si>
   <si>
-    <t xml:space="preserve">7.334e-2 (2)</t>
+    <t xml:space="preserve">6.041e-2 (3)</t>
   </si>
   <si>
     <t xml:space="preserve">5.282e-6 (9) </t>
   </si>
   <si>
-    <t xml:space="preserve">2.955e-8 (7)</t>
+    <t xml:space="preserve">6.773e-6 (7)</t>
   </si>
   <si>
     <t xml:space="preserve">9.323e-3 (3)</t>
@@ -2067,13 +2070,12 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00E+00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2091,11 +2093,81 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b val="true"/>
+      <sz val="24"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF0000EE"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF006600"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF996600"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFCC0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -2103,10 +2175,9 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2115,8 +2186,50 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC0000"/>
+        <bgColor rgb="FF800000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF003300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF72BF44"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
     <fill>
@@ -2125,14 +2238,8 @@
         <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72BF44"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -2140,8 +2247,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="21">
+  <cellStyleXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2165,7 +2287,58 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2179,7 +2352,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2187,31 +2360,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="37" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2227,384 +2400,1141 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="24">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
     <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
     <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
     <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
-    <cellStyle name="Normal 2" xfId="20" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Heading" xfId="20" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Heading 1" xfId="21" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Heading 2" xfId="22" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Text" xfId="23" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Note" xfId="24" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Footnote" xfId="25" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Hyperlink" xfId="26" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Status" xfId="27" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Good" xfId="28" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Neutral" xfId="29" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Bad" xfId="30" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Warning" xfId="31" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Error" xfId="32" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Accent" xfId="33" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Accent 1" xfId="34" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Accent 2" xfId="35" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Accent 3" xfId="36" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Normal 2" xfId="37" builtinId="53" customBuiltin="true"/>
   </cellStyles>
-  <dxfs count="120">
+  <dxfs count="70">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <u val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <border diagonalUp="false" diagonalDown="false">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+      <protection locked="true" hidden="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -2613,14 +3543,14 @@
       <rgbColor rgb="FFFFFFFF"/>
       <rgbColor rgb="FFCC0000"/>
       <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF0000EE"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF006600"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF996600"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
@@ -2632,7 +3562,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -2656,7 +3586,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF72BF44"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF00B050"/>
       <rgbColor rgb="FF003300"/>
@@ -5622,7 +6552,7 @@
         <v>-0.00940969117188958</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
         <v>259</v>
       </c>
@@ -5777,7 +6707,7 @@
         <v>-0.00847489364886818</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G52" s="0" t="s">
         <v>269</v>
       </c>
@@ -12565,99 +13495,99 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q33:Q47 V33:V47">
-    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q48:Q62 V48:V62">
-    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+  <conditionalFormatting sqref="Q53:Q62 V53:V62 Q49:Q51 V49:V51">
+    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q63:Q77 V63:V77">
-    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q108:Q122 V108:V122">
-    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q123:Q137 V123:V137">
-    <cfRule type="duplicateValues" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q138:Q152 V138:V152">
-    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q153:Q167 V153:V167">
-    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3:S17 X3:X17">
-    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:S32 X18:X32">
-    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:S47 X33:X47">
-    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S48:S62 X48:X62">
-    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+  <conditionalFormatting sqref="S53:S62 X53:X62 S49:S51 X49:X51">
+    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S63:S77 X63:X77">
-    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S78:S92 X78:X92">
-    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S93:S107 X93:X107">
-    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S108:S122 X108:X122">
-    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S123:S137 X123:X137">
-    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S138:S152 X138:X152">
-    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S153:S167 X153:X167">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V1:V1048576 Q1:Q1048576">
+  <conditionalFormatting sqref="V53:V1048576 Q53:Q1048576 V1:V47 Q1:Q47 V49:V51 Q49:Q51">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12668,13 +13598,53 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V78:V92 Q78:Q92">
-    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V161 Q93:Q107 V93:V107">
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q52 V52">
+    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S52 X52">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V52 Q52">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q48 V48">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S48 X48">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V48 Q48">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -17166,145 +18136,145 @@
     <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:D129 I115:I129">
-    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D131:D145 I131:I145">
-    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D147:D161 I147:I161">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D163:D177 I163:I177">
-    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G17">
-    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:G33">
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G49">
-    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51:G65">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:G81">
-    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83:G97">
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G115:G129">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G131:G145">
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="29">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G147:G161">
-    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G163:G177">
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G171 G99:G113">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I17">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19:I33">
-    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
+    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I35:I49">
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I51:I65">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67:I81">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97 D83:D97">
-    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
+    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I99:I113">
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115:I129">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="42">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I131:I145">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="43">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I147:I161">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="44">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I163:I177">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21872,100 +22842,100 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:B33 G19:G33">
-    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35:B49 G35:G49">
-    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51:B65 G51:G65">
-    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67:B81 G67:G81">
-    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115:B129 G115:G129">
-    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B131:B145 G131:G145">
-    <cfRule type="duplicateValues" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147:B161 G147:G161">
-    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163:B177 G163:G177">
-    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D17 I3:I17">
-    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:D33 I19:I33">
-    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35:D49 I35:I49">
-    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:D65 I51:I65">
-    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:D81 I67:I81">
-    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:D97 I83:I97">
-    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D99:D113 I99:I113">
-    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:D129 I115:I129">
-    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D131:D145 I131:I145">
-    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D147:D161 I147:I161">
-    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D163:D177 I163:I177">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21980,12 +22950,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83:G97 B83:B97">
-    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G171 B99:B113 G99:G113">
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22000,7 +22970,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L7">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22013,7 +22983,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22026,7 +22996,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22039,7 +23009,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22223,6 +23193,7 @@
       <c r="AE2" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="AF2" s="3"/>
       <c r="AG2" s="8" t="s">
         <v>175</v>
       </c>
@@ -22232,6 +23203,7 @@
       <c r="AI2" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="AJ2" s="3"/>
       <c r="AK2" s="8" t="s">
         <v>516</v>
       </c>
@@ -22329,6 +23301,7 @@
       <c r="AE3" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="AF3" s="3"/>
       <c r="AG3" s="8" t="s">
         <v>121</v>
       </c>
@@ -22338,6 +23311,7 @@
       <c r="AI3" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="AJ3" s="3"/>
       <c r="AK3" s="8" t="s">
         <v>520</v>
       </c>
@@ -22435,6 +23409,7 @@
       <c r="AE4" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="AF4" s="3"/>
       <c r="AG4" s="8" t="s">
         <v>451</v>
       </c>
@@ -22444,6 +23419,7 @@
       <c r="AI4" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="AJ4" s="3"/>
       <c r="AK4" s="8" t="s">
         <v>525</v>
       </c>
@@ -22541,6 +23517,7 @@
       <c r="AE5" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="AF5" s="3"/>
       <c r="AG5" s="8" t="s">
         <v>98</v>
       </c>
@@ -22550,6 +23527,7 @@
       <c r="AI5" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="AJ5" s="3"/>
       <c r="AK5" s="8" t="s">
         <v>530</v>
       </c>
@@ -22647,6 +23625,7 @@
       <c r="AE6" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="AF6" s="3"/>
       <c r="AG6" s="8" t="s">
         <v>535</v>
       </c>
@@ -22656,6 +23635,7 @@
       <c r="AI6" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="AJ6" s="3"/>
       <c r="AK6" s="8" t="s">
         <v>502</v>
       </c>
@@ -22751,6 +23731,7 @@
       <c r="AE7" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="AF7" s="3"/>
       <c r="AG7" s="8" t="s">
         <v>161</v>
       </c>
@@ -22760,6 +23741,7 @@
       <c r="AI7" s="3" t="s">
         <v>98</v>
       </c>
+      <c r="AJ7" s="3"/>
       <c r="AK7" s="8" t="s">
         <v>539</v>
       </c>
@@ -22855,6 +23837,7 @@
       <c r="AE8" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="AF8" s="3"/>
       <c r="AG8" s="8" t="s">
         <v>545</v>
       </c>
@@ -22864,6 +23847,7 @@
       <c r="AI8" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="AJ8" s="3"/>
       <c r="AK8" s="8" t="s">
         <v>291</v>
       </c>
@@ -22957,6 +23941,7 @@
       <c r="AE9" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="AF9" s="3"/>
       <c r="AG9" s="8" t="s">
         <v>548</v>
       </c>
@@ -22966,6 +23951,7 @@
       <c r="AI9" s="3" t="s">
         <v>177</v>
       </c>
+      <c r="AJ9" s="3"/>
       <c r="AK9" s="8" t="s">
         <v>440</v>
       </c>
@@ -23059,6 +24045,7 @@
       <c r="AE10" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="AF10" s="3"/>
       <c r="AG10" s="8" t="s">
         <v>553</v>
       </c>
@@ -23068,6 +24055,7 @@
       <c r="AI10" s="3" t="s">
         <v>94</v>
       </c>
+      <c r="AJ10" s="3"/>
       <c r="AK10" s="8" t="s">
         <v>554</v>
       </c>
@@ -23159,6 +24147,7 @@
       <c r="AE11" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="AF11" s="3"/>
       <c r="AG11" s="8" t="s">
         <v>556</v>
       </c>
@@ -23168,6 +24157,7 @@
       <c r="AI11" s="3" t="s">
         <v>203</v>
       </c>
+      <c r="AJ11" s="3"/>
       <c r="AK11" s="8" t="s">
         <v>263</v>
       </c>
@@ -23259,6 +24249,7 @@
       <c r="AE12" s="3" t="s">
         <v>127</v>
       </c>
+      <c r="AF12" s="3"/>
       <c r="AG12" s="8" t="s">
         <v>560</v>
       </c>
@@ -23268,6 +24259,7 @@
       <c r="AI12" s="3" t="s">
         <v>286</v>
       </c>
+      <c r="AJ12" s="3"/>
       <c r="AK12" s="8" t="s">
         <v>561</v>
       </c>
@@ -23357,6 +24349,7 @@
       <c r="AE13" s="3" t="s">
         <v>85</v>
       </c>
+      <c r="AF13" s="3"/>
       <c r="AG13" s="8" t="s">
         <v>565</v>
       </c>
@@ -23366,6 +24359,7 @@
       <c r="AI13" s="3" t="s">
         <v>290</v>
       </c>
+      <c r="AJ13" s="3"/>
       <c r="AK13" s="8" t="s">
         <v>566</v>
       </c>
@@ -23455,6 +24449,7 @@
       <c r="AE14" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="AF14" s="3"/>
       <c r="AG14" s="8"/>
       <c r="AH14" s="3" t="s">
         <v>58</v>
@@ -23462,6 +24457,7 @@
       <c r="AI14" s="3" t="s">
         <v>293</v>
       </c>
+      <c r="AJ14" s="3"/>
       <c r="AK14" s="8" t="s">
         <v>571</v>
       </c>
@@ -23549,6 +24545,7 @@
       <c r="AE15" s="3" t="s">
         <v>54</v>
       </c>
+      <c r="AF15" s="3"/>
       <c r="AG15" s="8"/>
       <c r="AH15" s="3" t="s">
         <v>24</v>
@@ -23556,6 +24553,7 @@
       <c r="AI15" s="3" t="s">
         <v>297</v>
       </c>
+      <c r="AJ15" s="3"/>
       <c r="AK15" s="8" t="s">
         <v>524</v>
       </c>
@@ -23643,6 +24641,7 @@
       <c r="AE16" s="3" t="s">
         <v>177</v>
       </c>
+      <c r="AF16" s="3"/>
       <c r="AG16" s="8"/>
       <c r="AH16" s="3" t="s">
         <v>32</v>
@@ -23650,6 +24649,7 @@
       <c r="AI16" s="3" t="s">
         <v>127</v>
       </c>
+      <c r="AJ16" s="3"/>
       <c r="AK16" s="8" t="s">
         <v>576</v>
       </c>
@@ -24960,7 +25960,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:K44">
-    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24973,17 +25973,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K16">
-    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:O1048576">
-    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24996,17 +25996,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:P16">
-    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1:S1048576">
-    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25019,17 +26019,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:T16">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U1:W1048576">
-    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25042,17 +26042,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:X16">
-    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:AA1048576">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25065,17 +26065,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AB16">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AE1048576">
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25088,17 +26088,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AF16">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG1:AI1048576">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25111,17 +26111,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AJ16">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK1:AM1048576">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25136,35 +26136,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL16">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM2:AM16">
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO1:AQ1048576">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP16">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP10">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="29">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ16">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25268,10 +26268,10 @@
       <c r="F3" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>516</v>
       </c>
       <c r="I3" s="8" t="s">
@@ -25306,10 +26306,10 @@
       <c r="F4" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>520</v>
       </c>
       <c r="I4" s="8" t="s">
@@ -25344,10 +26344,10 @@
       <c r="F5" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>525</v>
       </c>
       <c r="I5" s="8" t="s">
@@ -25382,10 +26382,10 @@
       <c r="F6" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>530</v>
       </c>
       <c r="I6" s="8" t="s">
@@ -25420,10 +26420,10 @@
       <c r="F7" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>502</v>
       </c>
       <c r="I7" s="8" t="s">
@@ -25456,10 +26456,10 @@
       <c r="F8" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>539</v>
       </c>
       <c r="I8" s="8" t="s">
@@ -25492,10 +26492,10 @@
       <c r="F9" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>291</v>
       </c>
       <c r="I9" s="8" t="s">
@@ -25526,10 +26526,10 @@
       <c r="F10" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>440</v>
       </c>
       <c r="I10" s="8" t="s">
@@ -25560,10 +26560,10 @@
       <c r="F11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>554</v>
       </c>
       <c r="I11" s="8" t="s">
@@ -25592,10 +26592,10 @@
       <c r="F12" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>263</v>
       </c>
       <c r="I12" s="8" t="s">
@@ -25624,10 +26624,10 @@
       <c r="F13" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="8" t="s">
         <v>561</v>
       </c>
       <c r="I13" s="8" t="s">
@@ -25654,10 +26654,10 @@
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="8" t="s">
         <v>566</v>
       </c>
       <c r="I14" s="8" t="s">
@@ -25685,7 +26685,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="8" t="s">
         <v>571</v>
       </c>
       <c r="I15" s="8" t="s">
@@ -25711,7 +26711,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="8" t="s">
         <v>524</v>
       </c>
       <c r="I16" s="8" t="s">
@@ -25737,7 +26737,7 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>576</v>
       </c>
       <c r="I17" s="8" t="s">
@@ -25763,7 +26763,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="8" t="s">
         <v>579</v>
       </c>
       <c r="I18" s="8" t="s">
@@ -25789,7 +26789,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="8" t="s">
         <v>580</v>
       </c>
       <c r="I19" s="8" t="s">
@@ -25815,7 +26815,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="8" t="s">
         <v>583</v>
       </c>
       <c r="I20" s="8" t="s">
@@ -25841,7 +26841,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="8" t="s">
         <v>586</v>
       </c>
       <c r="I21" s="8" t="s">
@@ -25867,7 +26867,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="8" t="s">
         <v>494</v>
       </c>
       <c r="I22" s="8" t="s">
@@ -25891,7 +26891,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="8" t="s">
         <v>591</v>
       </c>
       <c r="I23" s="8" t="s">
@@ -25913,7 +26913,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="8" t="s">
         <v>62</v>
       </c>
       <c r="I24" s="8" t="s">
@@ -25935,7 +26935,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="8" t="s">
         <v>333</v>
       </c>
       <c r="I25" s="8" t="s">
@@ -25957,7 +26957,7 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="8" t="s">
         <v>595</v>
       </c>
       <c r="I26" s="8" t="s">
@@ -25979,7 +26979,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="8" t="s">
         <v>598</v>
       </c>
       <c r="I27" s="8" t="s">
@@ -26001,7 +27001,7 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="8" t="s">
         <v>601</v>
       </c>
       <c r="I28" s="8" t="s">
@@ -26023,7 +27023,7 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="8" t="s">
         <v>603</v>
       </c>
       <c r="I29" s="8" t="s">
@@ -26045,7 +27045,7 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="8" t="s">
         <v>606</v>
       </c>
       <c r="I30" s="8" t="s">
@@ -26067,7 +27067,7 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="8" t="s">
         <v>609</v>
       </c>
       <c r="I31" s="8" t="s">
@@ -26089,7 +27089,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="8" t="s">
         <v>611</v>
       </c>
       <c r="I32" s="8" t="s">
@@ -26111,7 +27111,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="8" t="s">
         <v>614</v>
       </c>
       <c r="I33" s="8" t="s">
@@ -26131,7 +27131,7 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="8" t="s">
         <v>617</v>
       </c>
       <c r="I34" s="8" t="s">
@@ -26151,7 +27151,7 @@
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="8" t="s">
         <v>620</v>
       </c>
       <c r="I35" s="8" t="s">
@@ -26370,6 +27370,11 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:J45">
     <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G14 H3:H35">
+    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26388,7 +27393,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.67"/>
@@ -26422,8 +27427,7 @@
       <c r="L1" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>656</v>
       </c>
     </row>
@@ -26458,12 +27462,7 @@
       <c r="K2" s="13" t="s">
         <v>658</v>
       </c>
-      <c r="L2" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>658</v>
-      </c>
+      <c r="L2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
@@ -26472,7 +27471,7 @@
       <c r="L3" s="14" t="s">
         <v>659</v>
       </c>
-      <c r="N3" s="0" t="s">
+      <c r="M3" s="14" t="s">
         <v>660</v>
       </c>
     </row>
@@ -26483,7 +27482,7 @@
       <c r="L4" s="14" t="s">
         <v>661</v>
       </c>
-      <c r="N4" s="0" t="s">
+      <c r="M4" s="14" t="s">
         <v>662</v>
       </c>
     </row>
@@ -26491,18 +27490,19 @@
       <c r="A5" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="L5" s="14" t="s">
         <v>663</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>259</v>
       </c>
-      <c r="M6" s="0" t="s">
-        <v>664</v>
-      </c>
-      <c r="N6" s="14" t="s">
+      <c r="L6" s="14"/>
+      <c r="M6" s="14" t="s">
         <v>665</v>
       </c>
     </row>
@@ -26510,24 +27510,29 @@
       <c r="A7" s="0" t="s">
         <v>302</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="L7" s="14" t="s">
         <v>666</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>347</v>
       </c>
-      <c r="N8" s="14" t="s">
-        <v>667</v>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>379</v>
       </c>
-      <c r="N9" s="15" t="s">
-        <v>668</v>
+      <c r="L9" s="14"/>
+      <c r="M9" s="15" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26535,10 +27540,10 @@
         <v>425</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="N10" s="0" t="s">
         <v>670</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26546,21 +27551,21 @@
         <v>455</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>671</v>
-      </c>
-      <c r="N11" s="0" t="s">
         <v>672</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>472</v>
       </c>
-      <c r="L12" s="0" t="s">
-        <v>673</v>
-      </c>
-      <c r="N12" s="14" t="s">
+      <c r="L12" s="14" t="s">
         <v>674</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26568,27 +27573,26 @@
         <v>490</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>675</v>
-      </c>
-      <c r="N13" s="0" t="s">
         <v>676</v>
       </c>
+      <c r="M13" s="14" t="s">
+        <v>677</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Arial,Regular"&amp;10&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Arial,Regular"&amp;10Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -26602,11 +27606,11 @@
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Arial,Regular"&amp;10&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Arial,Regular"&amp;10Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
+++ b/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3860" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3864" uniqueCount="682">
   <si>
     <t xml:space="preserve">class_name/model</t>
   </si>
@@ -1999,6 +1999,9 @@
     <t xml:space="preserve">bert</t>
   </si>
   <si>
+    <t xml:space="preserve">bert deep lift</t>
+  </si>
+  <si>
     <t xml:space="preserve">TOP</t>
   </si>
   <si>
@@ -2011,12 +2014,18 @@
     <t xml:space="preserve">1.465e-6 (6)</t>
   </si>
   <si>
+    <t xml:space="preserve">1.908e-5 (6)</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.972e-9 (9)</t>
   </si>
   <si>
     <t xml:space="preserve">4.066e-6 (5)</t>
   </si>
   <si>
+    <t xml:space="preserve">9.539e-12 (11)</t>
+  </si>
+  <si>
     <t xml:space="preserve">7.123e-2 (3)</t>
   </si>
   <si>
@@ -2024,6 +2033,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.082e-4 (4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856e-3 (5)</t>
   </si>
   <si>
     <t xml:space="preserve">7.889e-3 (4)</t>
@@ -2070,12 +2082,13 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00E+00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2094,137 +2107,19 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="24"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF808080"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="10"/>
-      <color rgb="FF0000EE"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF006600"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF996600"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFCC0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="3"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFCC"/>
-        <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
-        <bgColor rgb="FFDDDDDD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC0000"/>
-        <bgColor rgb="FF800000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FF003300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF808080"/>
-        <bgColor rgb="FF969696"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDDDDD"/>
-        <bgColor rgb="FFFFCCCC"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2239,7 +2134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -2247,23 +2142,8 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FF808080"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF808080"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF808080"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="38">
+  <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2287,57 +2167,6 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2352,7 +2181,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2360,36 +2189,40 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="37" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -2400,45 +2233,25 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="24">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
     <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
     <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
     <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
-    <cellStyle name="Heading" xfId="20" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Heading 1" xfId="21" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Heading 2" xfId="22" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Text" xfId="23" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Note" xfId="24" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Footnote" xfId="25" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Hyperlink" xfId="26" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Status" xfId="27" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Good" xfId="28" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Neutral" xfId="29" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Bad" xfId="30" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Warning" xfId="31" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Error" xfId="32" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Accent" xfId="33" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Accent 1" xfId="34" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Accent 2" xfId="35" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Accent 3" xfId="36" builtinId="53" customBuiltin="true"/>
-    <cellStyle name="Normal 2" xfId="37" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
-  <dxfs count="70">
+  <dxfs count="14">
     <dxf>
       <font>
         <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
@@ -2447,6 +2260,7 @@
     <dxf>
       <font>
         <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
@@ -2455,14 +2269,7 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <b val="0"/>
         <i val="0"/>
@@ -2491,6 +2298,7 @@
     <dxf>
       <font>
         <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <b val="0"/>
         <i val="0"/>
@@ -2519,6 +2327,25 @@
     <dxf>
       <font>
         <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <b val="0"/>
         <i val="0"/>
@@ -2547,62 +2374,7 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
@@ -2611,6 +2383,7 @@
     <dxf>
       <font>
         <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
@@ -2619,6 +2392,7 @@
     <dxf>
       <font>
         <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
@@ -2627,6 +2401,7 @@
     <dxf>
       <font>
         <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
@@ -2635,34 +2410,7 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
@@ -2671,6 +2419,7 @@
     <dxf>
       <font>
         <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
@@ -2679,878 +2428,27 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
+        <charset val="1"/>
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
-      <protection locked="true" hidden="false"/>
     </dxf>
   </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFCC0000"/>
+      <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000EE"/>
+      <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF006600"/>
+      <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF996600"/>
+      <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
@@ -3562,7 +2460,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFDDDDDD"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -3578,7 +2476,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCCCC"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF92D050"/>
@@ -13490,100 +12388,100 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q18:Q32 V18:V32">
-    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q33:Q47 V33:V47">
-    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q53:Q62 V53:V62 Q49:Q51 V49:V51">
-    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q63:Q77 V63:V77">
-    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q108:Q122 V108:V122">
-    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q123:Q137 V123:V137">
-    <cfRule type="duplicateValues" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q138:Q152 V138:V152">
-    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q153:Q167 V153:V167">
-    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3:S17 X3:X17">
-    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:S32 X18:X32">
-    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:S47 X33:X47">
-    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S53:S62 X53:X62 S49:S51 X49:X51">
-    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S63:S77 X63:X77">
-    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S78:S92 X78:X92">
-    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S93:S107 X93:X107">
-    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S108:S122 X108:X122">
-    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S123:S137 X123:X137">
-    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S138:S152 X138:X152">
-    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S153:S167 X153:X167">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13598,22 +12496,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V78:V92 Q78:Q92">
-    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V161 Q93:Q107 V93:V107">
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q52 V52">
-    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S52 X52">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13628,12 +12526,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q48 V48">
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S48 X48">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13668,11 +12566,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="11" style="0" width="8.67"/>
@@ -18058,223 +16956,223 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:B33 G19:G33">
-    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35:B49 G35:G49">
-    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51:B65 G51:G65">
-    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67:B81 G67:G81">
-    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B83:B97 G83:G97">
-    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:B113 G99:G113">
-    <cfRule type="duplicateValues" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115:B129 G115:G129">
-    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B131:B145 G131:G145">
-    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147:B161 G147:G161">
-    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163:B177 G163:G177">
-    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D17 I3:I17">
-    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:D33 I19:I33">
-    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35:D49 I35:I49">
-    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:D65 I51:I65">
-    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:D81 I67:I81">
-    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D99:D113 I99:I113">
-    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:D129 I115:I129">
-    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D131:D145 I131:I145">
-    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D147:D161 I147:I161">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D163:D177 I163:I177">
-    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G17">
-    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:G33">
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G49">
-    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51:G65">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:G81">
-    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83:G97">
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G115:G129">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G131:G145">
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G147:G161">
-    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G163:G177">
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G171 G99:G113">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I17">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19:I33">
-    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I35:I49">
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I51:I65">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67:I81">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97 D83:D97">
-    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I99:I113">
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115:I129">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I131:I145">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I147:I161">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I163:I177">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22847,95 +21745,95 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35:B49 G35:G49">
-    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51:B65 G51:G65">
-    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67:B81 G67:G81">
-    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115:B129 G115:G129">
-    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B131:B145 G131:G145">
-    <cfRule type="duplicateValues" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147:B161 G147:G161">
-    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163:B177 G163:G177">
-    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D17 I3:I17">
-    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:D33 I19:I33">
-    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35:D49 I35:I49">
-    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:D65 I51:I65">
-    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:D81 I67:I81">
-    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:D97 I83:I97">
-    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D99:D113 I99:I113">
-    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:D129 I115:I129">
-    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D131:D145 I131:I145">
-    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D147:D161 I147:I161">
-    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D163:D177 I163:I177">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22950,12 +21848,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83:G97 B83:B97">
-    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G171 B99:B113 G99:G113">
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22970,7 +21868,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:L7">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22983,7 +21881,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22996,7 +21894,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23009,7 +21907,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23031,9 +21929,9 @@
   <dimension ref="A1:AR45"/>
   <sheetFormatPr defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="3" width="9.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="9.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="3" width="9.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="9.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="10.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="3" width="12.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="3" width="7.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="7.11"/>
@@ -23041,17 +21939,17 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="3" width="7.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="3" width="10.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="10.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="3" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="3" width="10.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="22" style="3" width="9.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="9.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="25" style="3" width="9.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="9.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="6.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="25" style="3" width="9.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="9.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="6.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="12.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="31" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="33" style="0" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="33" style="0" width="9.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="14.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="39" style="0" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="39" style="0" width="9.12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25932,12 +24830,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C16">
-    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:G16">
-    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25950,17 +24848,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G16">
-    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:K44">
-    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25973,17 +24871,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K16">
-    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:O1048576">
-    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25996,17 +24894,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:P16">
-    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1:S1048576">
-    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26019,17 +24917,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:T16">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U1:W1048576">
-    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26042,17 +24940,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:X16">
-    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:AA1048576">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26065,17 +24963,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AB16">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AE1048576">
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26088,17 +24986,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AF16">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG1:AI1048576">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26111,17 +25009,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AJ16">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK1:AM1048576">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26136,35 +25034,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL16">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM2:AM16">
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO1:AQ1048576">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP16">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP10">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ16">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26188,7 +25086,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.16"/>
@@ -27364,17 +26262,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A47 B3:B7">
-    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:J45">
-    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G14 H3:H35">
-    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="duplicateValues" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27393,11 +26291,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="21.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="15" style="0" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27424,159 +26326,171 @@
         <v>654</v>
       </c>
       <c r="K1" s="12"/>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="13" t="s">
         <v>656</v>
       </c>
+      <c r="N1" s="0" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>658</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="E2" s="13" t="s">
+      <c r="C2" s="14" t="s">
+        <v>659</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>658</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="G2" s="13" t="s">
+      <c r="E2" s="14" t="s">
+        <v>659</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>658</v>
       </c>
-      <c r="H2" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="I2" s="13" t="s">
+      <c r="G2" s="14" t="s">
+        <v>659</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>658</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="K2" s="13" t="s">
+      <c r="I2" s="14" t="s">
+        <v>659</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>658</v>
       </c>
-      <c r="L2" s="13"/>
+      <c r="K2" s="14" t="s">
+        <v>659</v>
+      </c>
+      <c r="L2" s="14"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="14" t="s">
-        <v>659</v>
-      </c>
-      <c r="M3" s="14" t="s">
+      <c r="L3" s="3" t="s">
         <v>660</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="N3" s="0" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="L4" s="14" t="s">
-        <v>661</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>662</v>
+      <c r="L4" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="N4" s="0" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="L5" s="14" t="s">
-        <v>663</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>664</v>
+      <c r="L5" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>259</v>
       </c>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14" t="s">
-        <v>665</v>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="N6" s="0" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>302</v>
       </c>
-      <c r="L7" s="14" t="s">
-        <v>666</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>667</v>
+      <c r="L7" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>347</v>
       </c>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14" t="s">
-        <v>668</v>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>379</v>
       </c>
-      <c r="L9" s="14"/>
+      <c r="L9" s="3"/>
       <c r="M9" s="15" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>425</v>
       </c>
-      <c r="L10" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="M10" s="14" t="s">
-        <v>671</v>
+      <c r="L10" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="L11" s="14" t="s">
-        <v>672</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>673</v>
+      <c r="L11" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>472</v>
       </c>
-      <c r="L12" s="14" t="s">
-        <v>674</v>
-      </c>
-      <c r="M12" s="14" t="s">
-        <v>675</v>
+      <c r="L12" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>679</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>490</v>
       </c>
-      <c r="L13" s="14" t="s">
-        <v>676</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>677</v>
+      <c r="L13" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -27604,6 +26518,9 @@
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="8.67"/>
+  </cols>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
+++ b/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3864" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3868" uniqueCount="684">
   <si>
     <t xml:space="preserve">class_name/model</t>
   </si>
@@ -2062,6 +2062,9 @@
     <t xml:space="preserve">3.967e-6 (4)</t>
   </si>
   <si>
+    <t xml:space="preserve">2.325e-4 (6)</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.041e-2 (3)</t>
   </si>
   <si>
@@ -2072,6 +2075,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.323e-3 (3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.988e-5 (6)</t>
   </si>
 </sst>
 </file>
@@ -26459,6 +26465,9 @@
       <c r="M10" s="3" t="s">
         <v>675</v>
       </c>
+      <c r="N10" s="0" t="s">
+        <v>674</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
@@ -26470,16 +26479,22 @@
       <c r="M11" s="3" t="s">
         <v>677</v>
       </c>
+      <c r="N11" s="0" t="s">
+        <v>678</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>472</v>
       </c>
       <c r="L12" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="N12" s="0" t="s">
         <v>678</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26487,10 +26502,13 @@
         <v>490</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
+      </c>
+      <c r="N13" s="0" t="s">
+        <v>683</v>
       </c>
     </row>
   </sheetData>

--- a/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
+++ b/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3868" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3876" uniqueCount="688">
   <si>
     <t xml:space="preserve">class_name/model</t>
   </si>
@@ -2002,6 +2002,9 @@
     <t xml:space="preserve">bert deep lift</t>
   </si>
   <si>
+    <t xml:space="preserve">bert IG</t>
+  </si>
+  <si>
     <t xml:space="preserve">TOP</t>
   </si>
   <si>
@@ -2047,6 +2050,9 @@
     <t xml:space="preserve">1.863e-6 (8)</t>
   </si>
   <si>
+    <t xml:space="preserve">1.083e-3 (5)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.638e-5 (4)</t>
   </si>
   <si>
@@ -2056,6 +2062,9 @@
     <t xml:space="preserve">6.967e-3 (3)</t>
   </si>
   <si>
+    <t xml:space="preserve">5.61e-9 (11)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.407e-5 (7)</t>
   </si>
   <si>
@@ -2063,6 +2072,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.325e-4 (6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.096e-6 (8)</t>
   </si>
   <si>
     <t xml:space="preserve">6.041e-2 (3)</t>
@@ -2253,7 +2265,7 @@
     <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
     <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="13">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -2261,7 +2273,6 @@
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2270,7 +2281,6 @@
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2288,10 +2298,9 @@
       <numFmt numFmtId="164" formatCode="General"/>
       <fill>
         <patternFill>
-          <bgColor rgb="00FFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <border diagonalUp="false" diagonalDown="false">
         <left/>
         <right/>
@@ -2299,7 +2308,6 @@
         <bottom/>
         <diagonal/>
       </border>
-      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2317,10 +2325,9 @@
       <numFmt numFmtId="164" formatCode="General"/>
       <fill>
         <patternFill>
-          <bgColor rgb="00FFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <border diagonalUp="false" diagonalDown="false">
         <left/>
         <right/>
@@ -2328,7 +2335,6 @@
         <bottom/>
         <diagonal/>
       </border>
-      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2337,7 +2343,6 @@
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2346,7 +2351,6 @@
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2364,10 +2368,9 @@
       <numFmt numFmtId="164" formatCode="General"/>
       <fill>
         <patternFill>
-          <bgColor rgb="00FFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <border diagonalUp="false" diagonalDown="false">
         <left/>
         <right/>
@@ -2375,7 +2378,6 @@
         <bottom/>
         <diagonal/>
       </border>
-      <protection locked="true" hidden="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2384,7 +2386,6 @@
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2393,7 +2394,6 @@
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2402,7 +2402,6 @@
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2411,7 +2410,6 @@
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2420,7 +2418,6 @@
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -2429,16 +2426,6 @@
         <family val="2"/>
         <color rgb="FF000000"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -12576,7 +12563,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="11" style="0" width="8.67"/>
@@ -17007,178 +16994,178 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B163:B177 G163:G177">
-    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D17 I3:I17">
-    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:D33 I19:I33">
-    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35:D49 I35:I49">
-    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:D65 I51:I65">
-    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:D81 I67:I81">
-    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D99:D113 I99:I113">
-    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:D129 I115:I129">
-    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D131:D145 I131:I145">
-    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D147:D161 I147:I161">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D163:D177 I163:I177">
-    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G17">
-    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:G33">
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G49">
-    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51:G65">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:G81">
-    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83:G97">
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G115:G129">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G131:G145">
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G147:G161">
-    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G163:G177">
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G171 G99:G113">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I17">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19:I33">
-    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I35:I49">
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I51:I65">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67:I81">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97 D83:D97">
-    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I99:I113">
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115:I129">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I131:I145">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I147:I161">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I163:I177">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21900,7 +21887,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21913,7 +21900,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21935,8 +21922,8 @@
   <dimension ref="A1:AR45"/>
   <sheetFormatPr defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="3" width="9.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="9.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="3" width="9.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="9.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="10.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="3" width="12.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="3" width="7.11"/>
@@ -21948,14 +21935,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="3" width="10.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="22" style="3" width="9.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="9.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="25" style="3" width="9.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="9.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="6.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="25" style="3" width="9.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="9.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="6.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="12.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="31" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="33" style="0" width="9.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="33" style="0" width="9.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="14.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="39" style="0" width="9.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="39" style="0" width="9.13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24928,12 +24915,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:T16">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U1:W1048576">
-    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24946,17 +24933,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:X16">
-    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:AA1048576">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24969,17 +24956,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AB16">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AE1048576">
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24992,17 +24979,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AF16">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG1:AI1048576">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25015,17 +25002,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AJ16">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK1:AM1048576">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25040,35 +25027,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL16">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM2:AM16">
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO1:AQ1048576">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP16">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP10">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ16">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26297,7 +26284,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.67"/>
@@ -26305,7 +26292,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="21.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="15" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="16" style="0" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26341,37 +26329,40 @@
       <c r="N1" s="0" t="s">
         <v>657</v>
       </c>
+      <c r="O1" s="0" t="s">
+        <v>658</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C2" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>659</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>658</v>
-      </c>
       <c r="E2" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>659</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>658</v>
-      </c>
       <c r="G2" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>659</v>
       </c>
-      <c r="H2" s="14" t="s">
-        <v>658</v>
-      </c>
       <c r="I2" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>659</v>
       </c>
-      <c r="J2" s="14" t="s">
-        <v>658</v>
-      </c>
       <c r="K2" s="14" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L2" s="14"/>
     </row>
@@ -26380,13 +26371,16 @@
         <v>11</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="N3" s="0" t="s">
+        <v>663</v>
+      </c>
+      <c r="O3" s="0" t="s">
         <v>661</v>
-      </c>
-      <c r="N3" s="0" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26394,13 +26388,16 @@
         <v>109</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="N4" s="0" t="s">
+        <v>666</v>
+      </c>
+      <c r="O4" s="0" t="s">
         <v>664</v>
-      </c>
-      <c r="N4" s="0" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26408,10 +26405,10 @@
         <v>178</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26420,10 +26417,10 @@
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26431,10 +26428,10 @@
         <v>302</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26443,7 +26440,10 @@
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
+      </c>
+      <c r="O8" s="0" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="15" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26460,13 +26460,16 @@
         <v>425</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>674</v>
+        <v>676</v>
+      </c>
+      <c r="O10" s="0" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26474,13 +26477,16 @@
         <v>455</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>678</v>
+        <v>681</v>
+      </c>
+      <c r="O11" s="0" t="s">
+        <v>682</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26488,13 +26494,16 @@
         <v>472</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="N12" s="0" t="s">
-        <v>678</v>
+        <v>681</v>
+      </c>
+      <c r="O12" s="0" t="s">
+        <v>683</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26502,13 +26511,16 @@
         <v>490</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="N13" s="0" t="s">
-        <v>683</v>
+        <v>687</v>
+      </c>
+      <c r="O13" s="0" t="s">
+        <v>687</v>
       </c>
     </row>
   </sheetData>

--- a/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
+++ b/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3876" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3871" uniqueCount="689">
   <si>
     <t xml:space="preserve">class_name/model</t>
   </si>
@@ -2005,10 +2005,7 @@
     <t xml:space="preserve">bert IG</t>
   </si>
   <si>
-    <t xml:space="preserve">TOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOTTOM</t>
+    <t xml:space="preserve">2.41e−4 (5)</t>
   </si>
   <si>
     <t xml:space="preserve">1.245e-6 (7)</t>
@@ -2020,6 +2017,9 @@
     <t xml:space="preserve">1.908e-5 (6)</t>
   </si>
   <si>
+    <t xml:space="preserve">2.022e-6 (7)</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.972e-9 (9)</t>
   </si>
   <si>
@@ -2065,15 +2065,15 @@
     <t xml:space="preserve">5.61e-9 (11)</t>
   </si>
   <si>
+    <t xml:space="preserve">2.325e-4 (6)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.407e-5 (7)</t>
   </si>
   <si>
     <t xml:space="preserve">3.967e-6 (4)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.325e-4 (6)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.096e-6 (8)</t>
   </si>
   <si>
@@ -2081,6 +2081,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.282e-6 (9) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.774e-4 (5)</t>
   </si>
   <si>
     <t xml:space="preserve">6.773e-6 (7)</t>
@@ -2190,7 +2193,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2251,6 +2254,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2265,7 +2272,7 @@
     <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
     <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="11">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -2378,22 +2385,6 @@
         <bottom/>
         <diagonal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -17014,158 +17005,158 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:D65 I51:I65">
-    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:D81 I67:I81">
-    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D99:D113 I99:I113">
-    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:D129 I115:I129">
-    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D131:D145 I131:I145">
-    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D147:D161 I147:I161">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D163:D177 I163:I177">
-    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G17">
-    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:G33">
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G49">
-    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51:G65">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:G81">
-    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83:G97">
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G115:G129">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G131:G145">
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G147:G161">
-    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G163:G177">
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G171 G99:G113">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I17">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19:I33">
-    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I35:I49">
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I51:I65">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67:I81">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97 D83:D97">
-    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I99:I113">
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115:I129">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I131:I145">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I147:I161">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I163:I177">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24943,7 +24934,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:AA1048576">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24956,17 +24947,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AB16">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AE1048576">
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24979,17 +24970,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AF16">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG1:AI1048576">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25002,17 +24993,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AJ16">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK1:AM1048576">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25027,35 +25018,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL16">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM2:AM16">
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO1:AQ1048576">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP16">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP10">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ16">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26284,16 +26275,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="21.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="16" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1019" min="11" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1020" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26303,100 +26296,76 @@
       <c r="B1" s="12" t="s">
         <v>650</v>
       </c>
-      <c r="C1" s="12"/>
+      <c r="C1" s="12" t="s">
+        <v>651</v>
+      </c>
       <c r="D1" s="12" t="s">
-        <v>651</v>
-      </c>
-      <c r="E1" s="12"/>
+        <v>652</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>653</v>
+      </c>
       <c r="F1" s="12" t="s">
-        <v>652</v>
-      </c>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12" t="s">
-        <v>653</v>
-      </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>656</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="I1" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="J1" s="0" t="s">
         <v>658</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="14" t="s">
-        <v>659</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>660</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>659</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>660</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>659</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>660</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>659</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>660</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>659</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>660</v>
-      </c>
-      <c r="L2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="B3" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="I3" s="0" t="s">
         <v>662</v>
       </c>
-      <c r="N3" s="0" t="s">
-        <v>663</v>
-      </c>
-      <c r="O3" s="0" t="s">
-        <v>661</v>
+      <c r="J3" s="0" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="B4" s="0" t="s">
+        <v>663</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="N4" s="0" t="s">
+      <c r="I4" s="0" t="s">
         <v>666</v>
       </c>
-      <c r="O4" s="0" t="s">
+      <c r="J4" s="0" t="s">
         <v>664</v>
       </c>
     </row>
@@ -26404,10 +26373,10 @@
       <c r="A5" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>668</v>
       </c>
     </row>
@@ -26415,11 +26384,11 @@
       <c r="A6" s="0" t="s">
         <v>259</v>
       </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3" t="s">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="N6" s="0" t="s">
+      <c r="I6" s="0" t="s">
         <v>670</v>
       </c>
     </row>
@@ -26427,10 +26396,10 @@
       <c r="A7" s="0" t="s">
         <v>302</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>672</v>
       </c>
     </row>
@@ -26438,11 +26407,11 @@
       <c r="A8" s="0" t="s">
         <v>347</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3" t="s">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="O8" s="0" t="s">
+      <c r="J8" s="0" t="s">
         <v>674</v>
       </c>
     </row>
@@ -26450,8 +26419,8 @@
       <c r="A9" s="0" t="s">
         <v>379</v>
       </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="15" t="s">
+      <c r="G9" s="3"/>
+      <c r="H9" s="16" t="s">
         <v>675</v>
       </c>
     </row>
@@ -26459,16 +26428,19 @@
       <c r="A10" s="0" t="s">
         <v>425</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="B10" s="0" t="s">
         <v>676</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="N10" s="0" t="s">
+      <c r="I10" s="0" t="s">
         <v>676</v>
       </c>
-      <c r="O10" s="0" t="s">
+      <c r="J10" s="0" t="s">
         <v>678</v>
       </c>
     </row>
@@ -26476,16 +26448,19 @@
       <c r="A11" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="B11" s="0" t="s">
         <v>679</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="N11" s="0" t="s">
+      <c r="H11" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="O11" s="0" t="s">
+      <c r="I11" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="J11" s="0" t="s">
         <v>682</v>
       </c>
     </row>
@@ -26493,16 +26468,16 @@
       <c r="A12" s="0" t="s">
         <v>472</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="N12" s="0" t="s">
-        <v>681</v>
-      </c>
-      <c r="O12" s="0" t="s">
+      <c r="I12" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="J12" s="0" t="s">
         <v>683</v>
       </c>
     </row>
@@ -26510,27 +26485,23 @@
       <c r="A13" s="0" t="s">
         <v>490</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="B13" s="0" t="s">
         <v>685</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="N13" s="0" t="s">
+      <c r="H13" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="O13" s="0" t="s">
-        <v>687</v>
+      <c r="I13" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>688</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
+++ b/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3871" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3951" uniqueCount="690">
   <si>
     <t xml:space="preserve">class_name/model</t>
   </si>
@@ -2093,6 +2093,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.988e-5 (6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bert g * I</t>
   </si>
 </sst>
 </file>
@@ -2272,151 +2275,33 @@
     <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
     <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="9">
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FF000000"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
   </dxfs>
   <colors>
@@ -17015,148 +16900,148 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D99:D113 I99:I113">
-    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D115:D129 I115:I129">
-    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D131:D145 I131:I145">
-    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D147:D161 I147:I161">
-    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D163:D177 I163:I177">
-    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G17">
-    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:G33">
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G49">
-    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51:G65">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:G81">
-    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83:G97">
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G115:G129">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G131:G145">
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G147:G161">
-    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G163:G177">
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G171 G99:G113">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I17">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19:I33">
-    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I35:I49">
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I51:I65">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67:I81">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97 D83:D97">
-    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I99:I113">
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115:I129">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I131:I145">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I147:I161">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I163:I177">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24952,12 +24837,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AB16">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AE1048576">
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24970,17 +24855,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AF16">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG1:AI1048576">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24993,17 +24878,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AJ16">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK1:AM1048576">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25018,35 +24903,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL16">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM2:AM16">
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO1:AQ1048576">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP16">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP10">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ16">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26275,12 +26160,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.55"/>
@@ -26498,6 +26386,283 @@
         <v>688</v>
       </c>
       <c r="J13" s="0" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>689</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>657</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>658</v>
+      </c>
+      <c r="F20" s="12"/>
+      <c r="G20" s="13" t="s">
+        <v>655</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>656</v>
+      </c>
+      <c r="I20" s="0" t="s">
+        <v>657</v>
+      </c>
+      <c r="J20" s="0" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>662</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>660</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="I22" s="0" t="s">
+        <v>662</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>663</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>666</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>664</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="I23" s="0" t="s">
+        <v>666</v>
+      </c>
+      <c r="J23" s="0" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="0" t="s">
+        <v>670</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="I25" s="0" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="E27" s="0" t="s">
+        <v>674</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="J27" s="0" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="16" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>676</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>676</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>678</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="I29" s="0" t="s">
+        <v>676</v>
+      </c>
+      <c r="J29" s="0" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>682</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="I30" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="J30" s="0" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>683</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="I31" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="J31" s="0" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>685</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="I32" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="J32" s="0" t="s">
         <v>688</v>
       </c>
     </row>

--- a/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
+++ b/cell_type_classification/results/all_top_bottom15_genes_all_classes.csv.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="all_top_bottom15_genes_all_clas" sheetId="1" state="visible" r:id="rId2"/>
@@ -14,7 +14,7 @@
     <sheet name="nn shap vs bert" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="bert" sheetId="5" state="visible" r:id="rId6"/>
     <sheet name="Sheet6" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="Sheet7" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="Sheet8" sheetId="7" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3951" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3994" uniqueCount="690">
   <si>
     <t xml:space="preserve">class_name/model</t>
   </si>
@@ -2275,34 +2275,14 @@
     <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
     <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-    </dxf>
+  <dxfs count="7">
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
   </dxfs>
   <colors>
     <indexedColors>
@@ -16933,115 +16913,115 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:G33">
-    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G49">
-    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51:G65">
-    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:G81">
-    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83:G97">
-    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G115:G129">
-    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G131:G145">
-    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G147:G161">
-    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G163:G177">
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G171 G99:G113">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I17">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19:I33">
-    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I35:I49">
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I51:I65">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67:I81">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97 D83:D97">
-    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:I97">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I99:I113">
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I115:I129">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I131:I145">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I147:I161">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I163:I177">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24855,17 +24835,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="duplicateValues" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AF16">
-    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG1:AI1048576">
-    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="duplicateValues" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24878,17 +24858,17 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI2:AJ16">
-    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="duplicateValues" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK1:AM1048576">
-    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24903,35 +24883,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL2:AL16">
-    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM2:AM16">
-    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="duplicateValues" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO1:AQ1048576">
-    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP2:AP16">
-    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP10">
-    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ2:AQ16">
-    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="duplicateValues" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26165,7 +26145,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.67"/>
@@ -26682,18 +26662,182 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.06"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>655</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>657</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>662</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>663</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>666</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="0" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="E8" s="0" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>676</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>676</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>685</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>688</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Arial,Regular"&amp;10&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Arial,Regular"&amp;10Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>